--- a/Excel/RelicConfig.xlsx
+++ b/Excel/RelicConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="28">
   <si>
     <t>#</t>
   </si>
@@ -44,13 +44,13 @@
     <t>Name</t>
   </si>
   <si>
-    <t>AttrId</t>
-  </si>
-  <si>
-    <t>AttrValue</t>
-  </si>
-  <si>
-    <t>AttrRise</t>
+    <t>AttrIdList</t>
+  </si>
+  <si>
+    <t>AttrValueList</t>
+  </si>
+  <si>
+    <t>AttrRiseList</t>
   </si>
   <si>
     <t>int</t>
@@ -62,34 +62,55 @@
     <t>int[]</t>
   </si>
   <si>
-    <t>青龙之剑</t>
-  </si>
-  <si>
-    <t>2001</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>青龙之甲</t>
+    <t>青龙神剑</t>
+  </si>
+  <si>
+    <t>2001,2002,2003,2004</t>
+  </si>
+  <si>
+    <t>20,30,40,20</t>
+  </si>
+  <si>
+    <t>青龙神甲</t>
+  </si>
+  <si>
+    <t>2001,2002,2003,2005</t>
   </si>
   <si>
     <t>青龙面罩</t>
   </si>
   <si>
+    <t>2001,2002,2003,2006</t>
+  </si>
+  <si>
     <t>青龙项链</t>
   </si>
   <si>
+    <t>2001,2002,2003,2007</t>
+  </si>
+  <si>
     <t>青龙护腕</t>
   </si>
   <si>
+    <t>2001,2002,2003,2008</t>
+  </si>
+  <si>
     <t>青龙护戒</t>
   </si>
   <si>
+    <t>2001,2002,2003,2009</t>
+  </si>
+  <si>
     <t>青龙腰带</t>
   </si>
   <si>
+    <t>2001,2002,2003,2010</t>
+  </si>
+  <si>
     <t>青龙战靴</t>
+  </si>
+  <si>
+    <t>2001,2002,2003,2012</t>
   </si>
 </sst>
 </file>
@@ -1069,7 +1090,9 @@
     <col min="1" max="4" width="9" style="1"/>
     <col min="5" max="5" width="9.75" style="1" customWidth="1"/>
     <col min="6" max="6" width="12.625" style="1" customWidth="1"/>
-    <col min="7" max="9" width="11.125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="22.375" style="1" customWidth="1"/>
+    <col min="8" max="8" width="17.75" style="1" customWidth="1"/>
+    <col min="9" max="9" width="18.25" style="1" customWidth="1"/>
     <col min="10" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -1171,8 +1194,8 @@
       <c r="H6" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="I6" s="2">
-        <v>0</v>
+      <c r="I6" s="6" t="s">
+        <v>13</v>
       </c>
       <c r="M6" s="4"/>
     </row>
@@ -1190,13 +1213,13 @@
         <v>14</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="H7" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="I7" s="2">
-        <v>0</v>
+      <c r="I7" s="6" t="s">
+        <v>13</v>
       </c>
       <c r="M7" s="4"/>
     </row>
@@ -1211,16 +1234,16 @@
         <v>61000003</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="H8" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="I8" s="2">
-        <v>0</v>
+      <c r="I8" s="6" t="s">
+        <v>13</v>
       </c>
       <c r="L8" s="2"/>
       <c r="M8" s="4"/>
@@ -1236,16 +1259,16 @@
         <v>61000004</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="H9" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="I9" s="2">
-        <v>0</v>
+      <c r="I9" s="6" t="s">
+        <v>13</v>
       </c>
       <c r="L9" s="2"/>
       <c r="M9" s="4"/>
@@ -1261,16 +1284,16 @@
         <v>61000005</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="H10" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="I10" s="2">
-        <v>0</v>
+      <c r="I10" s="6" t="s">
+        <v>13</v>
       </c>
       <c r="L10" s="2"/>
       <c r="M10" s="4"/>
@@ -1286,16 +1309,16 @@
         <v>61000006</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="H11" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="I11" s="2">
-        <v>0</v>
+      <c r="I11" s="6" t="s">
+        <v>13</v>
       </c>
       <c r="L11" s="2"/>
       <c r="M11" s="4"/>
@@ -1311,16 +1334,16 @@
         <v>61000007</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="H12" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="I12" s="2">
-        <v>0</v>
+      <c r="I12" s="6" t="s">
+        <v>13</v>
       </c>
       <c r="L12" s="2"/>
       <c r="M12" s="4"/>
@@ -1336,16 +1359,16 @@
         <v>61000008</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="H13" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="I13" s="2">
-        <v>0</v>
+      <c r="I13" s="6" t="s">
+        <v>13</v>
       </c>
       <c r="L13" s="2"/>
       <c r="M13" s="4"/>
@@ -1353,7 +1376,6 @@
     <row r="14" customHeight="1" spans="4:13">
       <c r="D14" s="2"/>
       <c r="E14" s="4"/>
-      <c r="F14" s="1"/>
       <c r="G14" s="2"/>
       <c r="H14" s="2"/>
       <c r="I14" s="2"/>
@@ -1363,7 +1385,6 @@
     <row r="15" customHeight="1" spans="4:13">
       <c r="D15" s="2"/>
       <c r="E15" s="4"/>
-      <c r="F15" s="1"/>
       <c r="G15" s="2"/>
       <c r="H15" s="2"/>
       <c r="I15" s="2"/>
@@ -1396,9 +1417,6 @@
       </c>
       <c r="E17" s="4"/>
       <c r="F17" s="1"/>
-      <c r="G17" s="2"/>
-      <c r="H17" s="2"/>
-      <c r="I17" s="2"/>
       <c r="M17" s="4"/>
     </row>
     <row r="18" customHeight="1" spans="1:13">
@@ -1415,7 +1433,6 @@
         <v>2</v>
       </c>
       <c r="E18" s="4"/>
-      <c r="F18" s="1"/>
       <c r="G18" s="2"/>
       <c r="H18" s="2"/>
       <c r="I18" s="2"/>
@@ -1437,9 +1454,6 @@
       </c>
       <c r="E19" s="4"/>
       <c r="F19" s="1"/>
-      <c r="G19" s="2"/>
-      <c r="H19" s="2"/>
-      <c r="I19" s="2"/>
       <c r="M19" s="4"/>
     </row>
     <row r="20" s="2" customFormat="1" customHeight="1" spans="1:13">
@@ -1457,9 +1471,6 @@
       </c>
       <c r="E20" s="4"/>
       <c r="F20" s="1"/>
-      <c r="G20" s="2"/>
-      <c r="H20" s="2"/>
-      <c r="I20" s="2"/>
       <c r="M20" s="4"/>
     </row>
     <row r="21" s="1" customFormat="1" customHeight="1" spans="1:13">
@@ -1476,7 +1487,6 @@
         <v>2</v>
       </c>
       <c r="E21" s="4"/>
-      <c r="F21" s="1"/>
       <c r="G21" s="2"/>
       <c r="H21" s="2"/>
       <c r="I21" s="2"/>
@@ -1663,7 +1673,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:D3 E3:F3 D4 E4:F4 D5 E5:F5 C4:C5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:F5" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/RelicConfig.xlsx
+++ b/Excel/RelicConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="定制配置" sheetId="2" r:id="rId1"/>
@@ -68,7 +68,7 @@
     <t>2001,2002,2003,2004</t>
   </si>
   <si>
-    <t>20,30,40,20</t>
+    <t>10,15,20,10</t>
   </si>
   <si>
     <t>青龙神甲</t>

--- a/Excel/RelicConfig.xlsx
+++ b/Excel/RelicConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680"/>
+    <workbookView windowWidth="27952" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="定制配置" sheetId="2" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="36">
   <si>
     <t>#</t>
   </si>
@@ -111,6 +111,30 @@
   </si>
   <si>
     <t>2001,2002,2003,2012</t>
+  </si>
+  <si>
+    <t>白虎神剑</t>
+  </si>
+  <si>
+    <t>白虎神甲</t>
+  </si>
+  <si>
+    <t>白虎面罩</t>
+  </si>
+  <si>
+    <t>白虎项链</t>
+  </si>
+  <si>
+    <t>白虎护腕</t>
+  </si>
+  <si>
+    <t>白虎护戒</t>
+  </si>
+  <si>
+    <t>白虎腰带</t>
+  </si>
+  <si>
+    <t>白虎战靴</t>
   </si>
 </sst>
 </file>
@@ -1088,11 +1112,11 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="4" width="9" style="1"/>
-    <col min="5" max="5" width="9.75" style="1" customWidth="1"/>
-    <col min="6" max="6" width="12.625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="22.375" style="1" customWidth="1"/>
-    <col min="8" max="8" width="17.75" style="1" customWidth="1"/>
-    <col min="9" max="9" width="18.25" style="1" customWidth="1"/>
+    <col min="5" max="5" width="9.75221238938053" style="1" customWidth="1"/>
+    <col min="6" max="6" width="12.6283185840708" style="1" customWidth="1"/>
+    <col min="7" max="7" width="22.3716814159292" style="1" customWidth="1"/>
+    <col min="8" max="8" width="17.7522123893805" style="1" customWidth="1"/>
+    <col min="9" max="9" width="18.2477876106195" style="1" customWidth="1"/>
     <col min="10" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -1402,147 +1426,208 @@
       <c r="L16" s="2"/>
       <c r="M16" s="4"/>
     </row>
-    <row r="17" s="2" customFormat="1" customHeight="1" spans="1:13">
-      <c r="A17" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>0</v>
-      </c>
+    <row r="17" s="2" customFormat="1" customHeight="1" spans="3:13">
       <c r="C17" s="2">
         <v>9</v>
       </c>
       <c r="D17" s="2">
         <v>2</v>
       </c>
-      <c r="E17" s="4"/>
-      <c r="F17" s="1"/>
+      <c r="E17" s="4">
+        <v>61000009</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G17" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="H17" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="I17" s="6" t="s">
+        <v>13</v>
+      </c>
       <c r="M17" s="4"/>
     </row>
     <row r="18" customHeight="1" spans="1:13">
-      <c r="A18" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>0</v>
-      </c>
+      <c r="A18" s="2"/>
+      <c r="B18" s="2"/>
       <c r="C18" s="2">
         <v>10</v>
       </c>
       <c r="D18" s="2">
         <v>2</v>
       </c>
-      <c r="E18" s="4"/>
-      <c r="G18" s="2"/>
-      <c r="H18" s="2"/>
-      <c r="I18" s="2"/>
+      <c r="E18" s="4">
+        <v>61000010</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G18" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="H18" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="I18" s="6" t="s">
+        <v>13</v>
+      </c>
       <c r="L18" s="2"/>
       <c r="M18" s="4"/>
     </row>
-    <row r="19" s="2" customFormat="1" customHeight="1" spans="1:13">
-      <c r="A19" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>0</v>
-      </c>
+    <row r="19" s="2" customFormat="1" customHeight="1" spans="3:13">
       <c r="C19" s="2">
         <v>11</v>
       </c>
       <c r="D19" s="2">
         <v>2</v>
       </c>
-      <c r="E19" s="4"/>
-      <c r="F19" s="1"/>
+      <c r="E19" s="4">
+        <v>61000011</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="G19" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="H19" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="I19" s="6" t="s">
+        <v>13</v>
+      </c>
       <c r="M19" s="4"/>
     </row>
-    <row r="20" s="2" customFormat="1" customHeight="1" spans="1:13">
-      <c r="A20" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>0</v>
-      </c>
+    <row r="20" s="2" customFormat="1" customHeight="1" spans="3:13">
       <c r="C20" s="2">
         <v>12</v>
       </c>
       <c r="D20" s="2">
         <v>2</v>
       </c>
-      <c r="E20" s="4"/>
-      <c r="F20" s="1"/>
+      <c r="E20" s="4">
+        <v>61000012</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="G20" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="H20" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="I20" s="6" t="s">
+        <v>13</v>
+      </c>
       <c r="M20" s="4"/>
     </row>
     <row r="21" s="1" customFormat="1" customHeight="1" spans="1:13">
-      <c r="A21" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>0</v>
-      </c>
+      <c r="A21" s="2"/>
+      <c r="B21" s="2"/>
       <c r="C21" s="2">
         <v>13</v>
       </c>
       <c r="D21" s="2">
         <v>2</v>
       </c>
-      <c r="E21" s="4"/>
-      <c r="G21" s="2"/>
-      <c r="H21" s="2"/>
-      <c r="I21" s="2"/>
+      <c r="E21" s="4">
+        <v>61000013</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="G21" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="H21" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="I21" s="6" t="s">
+        <v>13</v>
+      </c>
       <c r="L21" s="2"/>
       <c r="M21" s="4"/>
     </row>
     <row r="22" customHeight="1" spans="1:13">
-      <c r="A22" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>0</v>
-      </c>
+      <c r="A22" s="2"/>
+      <c r="B22" s="2"/>
       <c r="C22" s="2">
         <v>14</v>
       </c>
       <c r="D22" s="2">
         <v>2</v>
       </c>
+      <c r="E22" s="4">
+        <v>61000014</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="G22" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="H22" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="I22" s="6" t="s">
+        <v>13</v>
+      </c>
       <c r="L22" s="2"/>
       <c r="M22" s="4"/>
     </row>
-    <row r="23" s="2" customFormat="1" customHeight="1" spans="1:13">
-      <c r="A23" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>0</v>
-      </c>
+    <row r="23" s="2" customFormat="1" customHeight="1" spans="3:13">
       <c r="C23" s="2">
         <v>15</v>
       </c>
       <c r="D23" s="2">
         <v>2</v>
       </c>
-      <c r="E23" s="1"/>
-      <c r="F23" s="1"/>
-      <c r="G23" s="1"/>
-      <c r="H23" s="1"/>
-      <c r="I23" s="1"/>
+      <c r="E23" s="4">
+        <v>61000015</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="G23" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="H23" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="I23" s="6" t="s">
+        <v>13</v>
+      </c>
       <c r="J23" s="1"/>
       <c r="K23" s="1"/>
       <c r="M23" s="4"/>
     </row>
     <row r="24" customHeight="1" spans="1:13">
-      <c r="A24" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>0</v>
-      </c>
+      <c r="A24" s="2"/>
+      <c r="B24" s="2"/>
       <c r="C24" s="2">
         <v>16</v>
       </c>
       <c r="D24" s="2">
         <v>2</v>
+      </c>
+      <c r="E24" s="4">
+        <v>61000016</v>
+      </c>
+      <c r="F24" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="G24" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="H24" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="I24" s="6" t="s">
+        <v>13</v>
       </c>
       <c r="L24" s="2"/>
       <c r="M24" s="4"/>

--- a/Excel/RelicConfig.xlsx
+++ b/Excel/RelicConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="47">
   <si>
     <t>#</t>
   </si>
@@ -62,6 +62,9 @@
     <t>int[]</t>
   </si>
   <si>
+    <t>double[]</t>
+  </si>
+  <si>
     <t>青龙神剑</t>
   </si>
   <si>
@@ -135,6 +138,36 @@
   </si>
   <si>
     <t>白虎战靴</t>
+  </si>
+  <si>
+    <t>朱雀神剑</t>
+  </si>
+  <si>
+    <t>2001,2002,2003,32</t>
+  </si>
+  <si>
+    <t>10,15,20,0.5</t>
+  </si>
+  <si>
+    <t>朱雀神甲</t>
+  </si>
+  <si>
+    <t>朱雀面罩</t>
+  </si>
+  <si>
+    <t>朱雀项链</t>
+  </si>
+  <si>
+    <t>朱雀护腕</t>
+  </si>
+  <si>
+    <t>朱雀护戒</t>
+  </si>
+  <si>
+    <t>朱雀腰带</t>
+  </si>
+  <si>
+    <t>朱雀战靴</t>
   </si>
 </sst>
 </file>
@@ -1193,10 +1226,10 @@
         <v>10</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" s="2" customFormat="1" customHeight="1" spans="3:13">
@@ -1210,16 +1243,16 @@
         <v>61000001</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M6" s="4"/>
     </row>
@@ -1234,16 +1267,16 @@
         <v>61000002</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M7" s="4"/>
     </row>
@@ -1258,16 +1291,16 @@
         <v>61000003</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L8" s="2"/>
       <c r="M8" s="4"/>
@@ -1283,16 +1316,16 @@
         <v>61000004</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L9" s="2"/>
       <c r="M9" s="4"/>
@@ -1308,16 +1341,16 @@
         <v>61000005</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L10" s="2"/>
       <c r="M10" s="4"/>
@@ -1333,16 +1366,16 @@
         <v>61000006</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L11" s="2"/>
       <c r="M11" s="4"/>
@@ -1358,16 +1391,16 @@
         <v>61000007</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L12" s="2"/>
       <c r="M12" s="4"/>
@@ -1383,16 +1416,16 @@
         <v>61000008</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I13" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L13" s="2"/>
       <c r="M13" s="4"/>
@@ -1437,16 +1470,16 @@
         <v>61000009</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I17" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M17" s="4"/>
     </row>
@@ -1463,16 +1496,16 @@
         <v>61000010</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I18" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L18" s="2"/>
       <c r="M18" s="4"/>
@@ -1488,16 +1521,16 @@
         <v>61000011</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I19" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M19" s="4"/>
     </row>
@@ -1512,16 +1545,16 @@
         <v>61000012</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I20" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M20" s="4"/>
     </row>
@@ -1538,16 +1571,16 @@
         <v>61000013</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G21" s="6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H21" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I21" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L21" s="2"/>
       <c r="M21" s="4"/>
@@ -1565,16 +1598,16 @@
         <v>61000014</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I22" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L22" s="2"/>
       <c r="M22" s="4"/>
@@ -1590,16 +1623,16 @@
         <v>61000015</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G23" s="6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H23" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I23" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J23" s="1"/>
       <c r="K23" s="1"/>
@@ -1618,16 +1651,16 @@
         <v>61000016</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I24" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L24" s="2"/>
       <c r="M24" s="4"/>
@@ -1636,35 +1669,203 @@
       <c r="L25" s="2"/>
       <c r="M25" s="4"/>
     </row>
-    <row r="26" customHeight="1" spans="12:13">
+    <row r="26" customHeight="1" spans="3:13">
+      <c r="C26" s="2">
+        <v>17</v>
+      </c>
+      <c r="D26" s="2">
+        <v>3</v>
+      </c>
+      <c r="E26" s="4">
+        <v>61000017</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="G26" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="H26" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="I26" s="6" t="s">
+        <v>39</v>
+      </c>
       <c r="L26" s="2"/>
       <c r="M26" s="4"/>
     </row>
-    <row r="27" customHeight="1" spans="12:13">
+    <row r="27" customHeight="1" spans="3:13">
+      <c r="C27" s="2">
+        <v>18</v>
+      </c>
+      <c r="D27" s="2">
+        <v>3</v>
+      </c>
+      <c r="E27" s="4">
+        <v>61000018</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="G27" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="H27" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="I27" s="6" t="s">
+        <v>39</v>
+      </c>
       <c r="L27" s="2"/>
       <c r="M27" s="4"/>
     </row>
-    <row r="28" customHeight="1" spans="12:13">
+    <row r="28" customHeight="1" spans="3:13">
+      <c r="C28" s="2">
+        <v>19</v>
+      </c>
+      <c r="D28" s="2">
+        <v>3</v>
+      </c>
+      <c r="E28" s="4">
+        <v>61000019</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G28" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="H28" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="I28" s="6" t="s">
+        <v>39</v>
+      </c>
       <c r="L28" s="2"/>
       <c r="M28" s="4"/>
     </row>
-    <row r="29" customHeight="1" spans="12:13">
+    <row r="29" customHeight="1" spans="3:13">
+      <c r="C29" s="2">
+        <v>20</v>
+      </c>
+      <c r="D29" s="2">
+        <v>3</v>
+      </c>
+      <c r="E29" s="4">
+        <v>61000020</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G29" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="H29" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="I29" s="6" t="s">
+        <v>39</v>
+      </c>
       <c r="L29" s="2"/>
       <c r="M29" s="4"/>
     </row>
-    <row r="30" customHeight="1" spans="12:13">
+    <row r="30" customHeight="1" spans="3:13">
+      <c r="C30" s="2">
+        <v>21</v>
+      </c>
+      <c r="D30" s="2">
+        <v>3</v>
+      </c>
+      <c r="E30" s="4">
+        <v>61000021</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G30" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="H30" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="I30" s="6" t="s">
+        <v>39</v>
+      </c>
       <c r="L30" s="2"/>
       <c r="M30" s="4"/>
     </row>
-    <row r="31" customHeight="1" spans="12:13">
+    <row r="31" customHeight="1" spans="3:13">
+      <c r="C31" s="2">
+        <v>22</v>
+      </c>
+      <c r="D31" s="2">
+        <v>3</v>
+      </c>
+      <c r="E31" s="4">
+        <v>61000022</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="G31" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="H31" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="I31" s="6" t="s">
+        <v>39</v>
+      </c>
       <c r="L31" s="2"/>
       <c r="M31" s="4"/>
     </row>
-    <row r="32" customHeight="1" spans="12:13">
+    <row r="32" customHeight="1" spans="3:13">
+      <c r="C32" s="2">
+        <v>23</v>
+      </c>
+      <c r="D32" s="2">
+        <v>3</v>
+      </c>
+      <c r="E32" s="4">
+        <v>61000023</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="G32" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="H32" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="I32" s="6" t="s">
+        <v>39</v>
+      </c>
       <c r="L32" s="2"/>
       <c r="M32" s="4"/>
     </row>
-    <row r="33" customHeight="1" spans="12:13">
+    <row r="33" customHeight="1" spans="3:13">
+      <c r="C33" s="2">
+        <v>24</v>
+      </c>
+      <c r="D33" s="2">
+        <v>3</v>
+      </c>
+      <c r="E33" s="4">
+        <v>61000024</v>
+      </c>
+      <c r="F33" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="G33" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="H33" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="I33" s="6" t="s">
+        <v>39</v>
+      </c>
       <c r="L33" s="2"/>
       <c r="M33" s="4"/>
     </row>

--- a/Excel/RelicConfig.xlsx
+++ b/Excel/RelicConfig.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27952" windowHeight="12255"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="定制配置" sheetId="2" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="57">
   <si>
     <t>#</t>
   </si>
@@ -168,6 +168,36 @@
   </si>
   <si>
     <t>朱雀战靴</t>
+  </si>
+  <si>
+    <t>玄武神剑</t>
+  </si>
+  <si>
+    <t>2001,2002,2003,33</t>
+  </si>
+  <si>
+    <t>10,15,20,0.6</t>
+  </si>
+  <si>
+    <t>玄武神甲</t>
+  </si>
+  <si>
+    <t>玄武面罩</t>
+  </si>
+  <si>
+    <t>玄武项链</t>
+  </si>
+  <si>
+    <t>玄武护腕</t>
+  </si>
+  <si>
+    <t>玄武护戒</t>
+  </si>
+  <si>
+    <t>玄武腰带</t>
+  </si>
+  <si>
+    <t>玄武战靴</t>
   </si>
 </sst>
 </file>
@@ -1145,11 +1175,11 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="4" width="9" style="1"/>
-    <col min="5" max="5" width="9.75221238938053" style="1" customWidth="1"/>
-    <col min="6" max="6" width="12.6283185840708" style="1" customWidth="1"/>
-    <col min="7" max="7" width="22.3716814159292" style="1" customWidth="1"/>
-    <col min="8" max="8" width="17.7522123893805" style="1" customWidth="1"/>
-    <col min="9" max="9" width="18.2477876106195" style="1" customWidth="1"/>
+    <col min="5" max="5" width="9.75" style="1" customWidth="1"/>
+    <col min="6" max="6" width="12.625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="22.375" style="1" customWidth="1"/>
+    <col min="8" max="8" width="17.75" style="1" customWidth="1"/>
+    <col min="9" max="9" width="18.25" style="1" customWidth="1"/>
     <col min="10" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -1873,35 +1903,203 @@
       <c r="L34" s="2"/>
       <c r="M34" s="4"/>
     </row>
-    <row r="35" customHeight="1" spans="12:13">
+    <row r="35" customHeight="1" spans="3:13">
+      <c r="C35" s="2">
+        <v>25</v>
+      </c>
+      <c r="D35" s="2">
+        <v>4</v>
+      </c>
+      <c r="E35" s="4">
+        <v>61000017</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="G35" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="H35" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="I35" s="6" t="s">
+        <v>49</v>
+      </c>
       <c r="L35" s="2"/>
       <c r="M35" s="4"/>
     </row>
-    <row r="36" customHeight="1" spans="12:13">
+    <row r="36" customHeight="1" spans="3:13">
+      <c r="C36" s="2">
+        <v>26</v>
+      </c>
+      <c r="D36" s="2">
+        <v>4</v>
+      </c>
+      <c r="E36" s="4">
+        <v>61000018</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G36" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="H36" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="I36" s="6" t="s">
+        <v>49</v>
+      </c>
       <c r="L36" s="2"/>
       <c r="M36" s="4"/>
     </row>
-    <row r="37" customHeight="1" spans="12:13">
+    <row r="37" customHeight="1" spans="3:13">
+      <c r="C37" s="2">
+        <v>27</v>
+      </c>
+      <c r="D37" s="2">
+        <v>4</v>
+      </c>
+      <c r="E37" s="4">
+        <v>61000019</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="G37" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="H37" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="I37" s="6" t="s">
+        <v>49</v>
+      </c>
       <c r="L37" s="2"/>
       <c r="M37" s="4"/>
     </row>
-    <row r="38" customHeight="1" spans="12:13">
+    <row r="38" customHeight="1" spans="3:13">
+      <c r="C38" s="2">
+        <v>28</v>
+      </c>
+      <c r="D38" s="2">
+        <v>4</v>
+      </c>
+      <c r="E38" s="4">
+        <v>61000020</v>
+      </c>
+      <c r="F38" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="G38" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="H38" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="I38" s="6" t="s">
+        <v>49</v>
+      </c>
       <c r="L38" s="2"/>
       <c r="M38" s="4"/>
     </row>
-    <row r="39" customHeight="1" spans="12:13">
+    <row r="39" customHeight="1" spans="3:13">
+      <c r="C39" s="2">
+        <v>29</v>
+      </c>
+      <c r="D39" s="2">
+        <v>4</v>
+      </c>
+      <c r="E39" s="4">
+        <v>61000021</v>
+      </c>
+      <c r="F39" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="G39" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="H39" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="I39" s="6" t="s">
+        <v>49</v>
+      </c>
       <c r="L39" s="2"/>
       <c r="M39" s="4"/>
     </row>
-    <row r="40" customHeight="1" spans="12:13">
+    <row r="40" customHeight="1" spans="3:13">
+      <c r="C40" s="2">
+        <v>30</v>
+      </c>
+      <c r="D40" s="2">
+        <v>4</v>
+      </c>
+      <c r="E40" s="4">
+        <v>61000022</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="G40" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="H40" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="I40" s="6" t="s">
+        <v>49</v>
+      </c>
       <c r="L40" s="2"/>
       <c r="M40" s="4"/>
     </row>
-    <row r="41" customHeight="1" spans="12:13">
+    <row r="41" customHeight="1" spans="3:13">
+      <c r="C41" s="2">
+        <v>31</v>
+      </c>
+      <c r="D41" s="2">
+        <v>4</v>
+      </c>
+      <c r="E41" s="4">
+        <v>61000023</v>
+      </c>
+      <c r="F41" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="G41" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="H41" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="I41" s="6" t="s">
+        <v>49</v>
+      </c>
       <c r="L41" s="2"/>
       <c r="M41" s="4"/>
     </row>
-    <row r="42" customHeight="1" spans="12:13">
+    <row r="42" customHeight="1" spans="3:13">
+      <c r="C42" s="2">
+        <v>32</v>
+      </c>
+      <c r="D42" s="2">
+        <v>4</v>
+      </c>
+      <c r="E42" s="4">
+        <v>61000024</v>
+      </c>
+      <c r="F42" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="G42" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="H42" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="I42" s="6" t="s">
+        <v>49</v>
+      </c>
       <c r="L42" s="2"/>
       <c r="M42" s="4"/>
     </row>

--- a/Excel/RelicConfig.xlsx
+++ b/Excel/RelicConfig.xlsx
@@ -173,7 +173,7 @@
     <t>玄武神剑</t>
   </si>
   <si>
-    <t>2001,2002,2003,33</t>
+    <t>2001,2002,2003,31</t>
   </si>
   <si>
     <t>10,15,20,0.6</t>
@@ -1911,7 +1911,7 @@
         <v>4</v>
       </c>
       <c r="E35" s="4">
-        <v>61000017</v>
+        <v>61000025</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>47</v>
@@ -1936,7 +1936,7 @@
         <v>4</v>
       </c>
       <c r="E36" s="4">
-        <v>61000018</v>
+        <v>61000026</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>50</v>
@@ -1961,7 +1961,7 @@
         <v>4</v>
       </c>
       <c r="E37" s="4">
-        <v>61000019</v>
+        <v>61000027</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>51</v>
@@ -1986,7 +1986,7 @@
         <v>4</v>
       </c>
       <c r="E38" s="4">
-        <v>61000020</v>
+        <v>61000028</v>
       </c>
       <c r="F38" s="1" t="s">
         <v>52</v>
@@ -2011,7 +2011,7 @@
         <v>4</v>
       </c>
       <c r="E39" s="4">
-        <v>61000021</v>
+        <v>61000029</v>
       </c>
       <c r="F39" s="1" t="s">
         <v>53</v>
@@ -2036,7 +2036,7 @@
         <v>4</v>
       </c>
       <c r="E40" s="4">
-        <v>61000022</v>
+        <v>61000030</v>
       </c>
       <c r="F40" s="1" t="s">
         <v>54</v>
@@ -2061,7 +2061,7 @@
         <v>4</v>
       </c>
       <c r="E41" s="4">
-        <v>61000023</v>
+        <v>61000031</v>
       </c>
       <c r="F41" s="1" t="s">
         <v>55</v>
@@ -2086,7 +2086,7 @@
         <v>4</v>
       </c>
       <c r="E42" s="4">
-        <v>61000024</v>
+        <v>61000032</v>
       </c>
       <c r="F42" s="5" t="s">
         <v>56</v>

--- a/Excel/RelicConfig.xlsx
+++ b/Excel/RelicConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="67">
   <si>
     <t>#</t>
   </si>
@@ -198,6 +198,36 @@
   </si>
   <si>
     <t>玄武战靴</t>
+  </si>
+  <si>
+    <t>麒麟神剑</t>
+  </si>
+  <si>
+    <t>2001,2002,2003,2013</t>
+  </si>
+  <si>
+    <t>10,15,20,20</t>
+  </si>
+  <si>
+    <t>麒麟神甲</t>
+  </si>
+  <si>
+    <t>麒麟面罩</t>
+  </si>
+  <si>
+    <t>麒麟项链</t>
+  </si>
+  <si>
+    <t>麒麟护腕</t>
+  </si>
+  <si>
+    <t>麒麟护戒</t>
+  </si>
+  <si>
+    <t>麒麟腰带</t>
+  </si>
+  <si>
+    <t>麒麟战靴</t>
   </si>
 </sst>
 </file>
@@ -1183,17 +1213,17 @@
     <col min="10" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" customHeight="1" spans="10:10">
+    <row r="1" customHeight="1" spans="3:13">
       <c r="J1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" customHeight="1" spans="10:10">
+    <row r="2" customHeight="1" spans="3:13">
       <c r="J2" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:9">
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:13">
       <c r="C3" s="3" t="s">
         <v>1</v>
       </c>
@@ -1216,7 +1246,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:9">
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:13">
       <c r="C4" s="3" t="s">
         <v>1</v>
       </c>
@@ -1239,7 +1269,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:9">
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:13">
       <c r="C5" s="3" t="s">
         <v>8</v>
       </c>
@@ -1460,7 +1490,7 @@
       <c r="L13" s="2"/>
       <c r="M13" s="4"/>
     </row>
-    <row r="14" customHeight="1" spans="4:13">
+    <row r="14" customHeight="1" spans="3:13">
       <c r="D14" s="2"/>
       <c r="E14" s="4"/>
       <c r="G14" s="2"/>
@@ -1469,7 +1499,7 @@
       <c r="L14" s="2"/>
       <c r="M14" s="4"/>
     </row>
-    <row r="15" customHeight="1" spans="4:13">
+    <row r="15" customHeight="1" spans="3:13">
       <c r="D15" s="2"/>
       <c r="E15" s="4"/>
       <c r="G15" s="2"/>
@@ -1489,7 +1519,7 @@
       <c r="L16" s="2"/>
       <c r="M16" s="4"/>
     </row>
-    <row r="17" s="2" customFormat="1" customHeight="1" spans="3:13">
+    <row r="17" s="2" customFormat="1" customHeight="1" spans="1:13">
       <c r="C17" s="2">
         <v>9</v>
       </c>
@@ -1540,7 +1570,7 @@
       <c r="L18" s="2"/>
       <c r="M18" s="4"/>
     </row>
-    <row r="19" s="2" customFormat="1" customHeight="1" spans="3:13">
+    <row r="19" s="2" customFormat="1" customHeight="1" spans="1:13">
       <c r="C19" s="2">
         <v>11</v>
       </c>
@@ -1564,7 +1594,7 @@
       </c>
       <c r="M19" s="4"/>
     </row>
-    <row r="20" s="2" customFormat="1" customHeight="1" spans="3:13">
+    <row r="20" s="2" customFormat="1" customHeight="1" spans="1:13">
       <c r="C20" s="2">
         <v>12</v>
       </c>
@@ -1642,7 +1672,7 @@
       <c r="L22" s="2"/>
       <c r="M22" s="4"/>
     </row>
-    <row r="23" s="2" customFormat="1" customHeight="1" spans="3:13">
+    <row r="23" s="2" customFormat="1" customHeight="1" spans="1:13">
       <c r="C23" s="2">
         <v>15</v>
       </c>
@@ -1695,11 +1725,11 @@
       <c r="L24" s="2"/>
       <c r="M24" s="4"/>
     </row>
-    <row r="25" customHeight="1" spans="12:13">
+    <row r="25" customHeight="1" spans="1:13">
       <c r="L25" s="2"/>
       <c r="M25" s="4"/>
     </row>
-    <row r="26" customHeight="1" spans="3:13">
+    <row r="26" customHeight="1" spans="1:13">
       <c r="C26" s="2">
         <v>17</v>
       </c>
@@ -1724,7 +1754,7 @@
       <c r="L26" s="2"/>
       <c r="M26" s="4"/>
     </row>
-    <row r="27" customHeight="1" spans="3:13">
+    <row r="27" customHeight="1" spans="1:13">
       <c r="C27" s="2">
         <v>18</v>
       </c>
@@ -1749,7 +1779,7 @@
       <c r="L27" s="2"/>
       <c r="M27" s="4"/>
     </row>
-    <row r="28" customHeight="1" spans="3:13">
+    <row r="28" customHeight="1" spans="1:13">
       <c r="C28" s="2">
         <v>19</v>
       </c>
@@ -1774,7 +1804,7 @@
       <c r="L28" s="2"/>
       <c r="M28" s="4"/>
     </row>
-    <row r="29" customHeight="1" spans="3:13">
+    <row r="29" customHeight="1" spans="1:13">
       <c r="C29" s="2">
         <v>20</v>
       </c>
@@ -1799,7 +1829,7 @@
       <c r="L29" s="2"/>
       <c r="M29" s="4"/>
     </row>
-    <row r="30" customHeight="1" spans="3:13">
+    <row r="30" customHeight="1" spans="1:13">
       <c r="C30" s="2">
         <v>21</v>
       </c>
@@ -1824,7 +1854,7 @@
       <c r="L30" s="2"/>
       <c r="M30" s="4"/>
     </row>
-    <row r="31" customHeight="1" spans="3:13">
+    <row r="31" customHeight="1" spans="1:13">
       <c r="C31" s="2">
         <v>22</v>
       </c>
@@ -1849,7 +1879,7 @@
       <c r="L31" s="2"/>
       <c r="M31" s="4"/>
     </row>
-    <row r="32" customHeight="1" spans="3:13">
+    <row r="32" customHeight="1" spans="1:13">
       <c r="C32" s="2">
         <v>23</v>
       </c>
@@ -1899,7 +1929,7 @@
       <c r="L33" s="2"/>
       <c r="M33" s="4"/>
     </row>
-    <row r="34" customHeight="1" spans="12:13">
+    <row r="34" customHeight="1" spans="3:13">
       <c r="L34" s="2"/>
       <c r="M34" s="4"/>
     </row>
@@ -2103,55 +2133,223 @@
       <c r="L42" s="2"/>
       <c r="M42" s="4"/>
     </row>
-    <row r="43" customHeight="1" spans="12:13">
+    <row r="43" customHeight="1" spans="3:13">
       <c r="L43" s="2"/>
       <c r="M43" s="4"/>
     </row>
-    <row r="44" customHeight="1" spans="12:13">
+    <row r="44" customHeight="1" spans="3:13">
+      <c r="C44" s="2">
+        <v>33</v>
+      </c>
+      <c r="D44" s="2">
+        <v>5</v>
+      </c>
+      <c r="E44" s="4">
+        <v>61000033</v>
+      </c>
+      <c r="F44" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="G44" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="H44" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="I44" s="6" t="s">
+        <v>59</v>
+      </c>
       <c r="L44" s="2"/>
       <c r="M44" s="4"/>
     </row>
-    <row r="45" customHeight="1" spans="12:13">
+    <row r="45" customHeight="1" spans="3:13">
+      <c r="C45" s="2">
+        <v>34</v>
+      </c>
+      <c r="D45" s="2">
+        <v>5</v>
+      </c>
+      <c r="E45" s="4">
+        <v>61000034</v>
+      </c>
+      <c r="F45" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="G45" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="H45" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="I45" s="6" t="s">
+        <v>59</v>
+      </c>
       <c r="L45" s="2"/>
       <c r="M45" s="4"/>
     </row>
-    <row r="46" customHeight="1" spans="12:13">
+    <row r="46" customHeight="1" spans="3:13">
+      <c r="C46" s="2">
+        <v>35</v>
+      </c>
+      <c r="D46" s="2">
+        <v>5</v>
+      </c>
+      <c r="E46" s="4">
+        <v>61000035</v>
+      </c>
+      <c r="F46" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="G46" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="H46" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="I46" s="6" t="s">
+        <v>59</v>
+      </c>
       <c r="L46" s="2"/>
       <c r="M46" s="4"/>
     </row>
-    <row r="47" customHeight="1" spans="12:13">
+    <row r="47" customHeight="1" spans="3:13">
+      <c r="C47" s="2">
+        <v>36</v>
+      </c>
+      <c r="D47" s="2">
+        <v>5</v>
+      </c>
+      <c r="E47" s="4">
+        <v>61000036</v>
+      </c>
+      <c r="F47" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="G47" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="H47" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="I47" s="6" t="s">
+        <v>59</v>
+      </c>
       <c r="L47" s="2"/>
       <c r="M47" s="4"/>
     </row>
-    <row r="48" customHeight="1" spans="12:13">
+    <row r="48" customHeight="1" spans="3:13">
+      <c r="C48" s="2">
+        <v>37</v>
+      </c>
+      <c r="D48" s="2">
+        <v>5</v>
+      </c>
+      <c r="E48" s="4">
+        <v>61000037</v>
+      </c>
+      <c r="F48" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="G48" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="H48" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="I48" s="6" t="s">
+        <v>59</v>
+      </c>
       <c r="L48" s="2"/>
       <c r="M48" s="4"/>
     </row>
-    <row r="49" customHeight="1" spans="12:13">
+    <row r="49" customHeight="1" spans="3:13">
+      <c r="C49" s="2">
+        <v>38</v>
+      </c>
+      <c r="D49" s="2">
+        <v>5</v>
+      </c>
+      <c r="E49" s="4">
+        <v>61000038</v>
+      </c>
+      <c r="F49" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="G49" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="H49" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="I49" s="6" t="s">
+        <v>59</v>
+      </c>
       <c r="L49" s="2"/>
       <c r="M49" s="4"/>
     </row>
-    <row r="50" customHeight="1" spans="12:13">
+    <row r="50" customHeight="1" spans="3:13">
+      <c r="C50" s="2">
+        <v>39</v>
+      </c>
+      <c r="D50" s="2">
+        <v>5</v>
+      </c>
+      <c r="E50" s="4">
+        <v>61000039</v>
+      </c>
+      <c r="F50" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="G50" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="H50" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="I50" s="6" t="s">
+        <v>59</v>
+      </c>
       <c r="L50" s="2"/>
       <c r="M50" s="4"/>
     </row>
-    <row r="51" customHeight="1" spans="12:13">
+    <row r="51" customHeight="1" spans="3:13">
+      <c r="C51" s="2">
+        <v>40</v>
+      </c>
+      <c r="D51" s="2">
+        <v>5</v>
+      </c>
+      <c r="E51" s="4">
+        <v>61000040</v>
+      </c>
+      <c r="F51" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="G51" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="H51" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="I51" s="6" t="s">
+        <v>59</v>
+      </c>
       <c r="L51" s="2"/>
       <c r="M51" s="4"/>
     </row>
-    <row r="52" customHeight="1" spans="12:13">
+    <row r="52" customHeight="1" spans="3:13">
       <c r="L52" s="2"/>
       <c r="M52" s="4"/>
     </row>
-    <row r="53" customHeight="1" spans="12:13">
+    <row r="53" customHeight="1" spans="3:13">
       <c r="L53" s="2"/>
       <c r="M53" s="4"/>
     </row>
-    <row r="54" customHeight="1" spans="12:13">
+    <row r="54" customHeight="1" spans="3:13">
       <c r="L54" s="2"/>
       <c r="M54" s="4"/>
     </row>
-    <row r="55" customHeight="1" spans="12:13">
+    <row r="55" customHeight="1" spans="3:13">
       <c r="L55" s="2"/>
       <c r="M55" s="4"/>
     </row>

--- a/Excel/RelicConfig.xlsx
+++ b/Excel/RelicConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="78">
   <si>
     <t>#</t>
   </si>
@@ -38,6 +38,9 @@
     <t>Type</t>
   </si>
   <si>
+    <t>Cycle</t>
+  </si>
+  <si>
     <t>ItemId</t>
   </si>
   <si>
@@ -228,6 +231,36 @@
   </si>
   <si>
     <t>麒麟战靴</t>
+  </si>
+  <si>
+    <t>极龙神剑</t>
+  </si>
+  <si>
+    <t>2001,2012,2003,2013</t>
+  </si>
+  <si>
+    <t>15,20,25,15</t>
+  </si>
+  <si>
+    <t>极龙神甲</t>
+  </si>
+  <si>
+    <t>极龙面罩</t>
+  </si>
+  <si>
+    <t>极龙项链</t>
+  </si>
+  <si>
+    <t>极龙护腕</t>
+  </si>
+  <si>
+    <t>极龙护戒</t>
+  </si>
+  <si>
+    <t>极龙腰带</t>
+  </si>
+  <si>
+    <t>极龙战靴</t>
   </si>
 </sst>
 </file>
@@ -1201,29 +1234,29 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M55"/>
+  <dimension ref="A1:N60"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
-    <col min="1" max="4" width="9" style="1"/>
-    <col min="5" max="5" width="9.75" style="1" customWidth="1"/>
-    <col min="6" max="6" width="12.625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="22.375" style="1" customWidth="1"/>
-    <col min="8" max="8" width="17.75" style="1" customWidth="1"/>
-    <col min="9" max="9" width="18.25" style="1" customWidth="1"/>
-    <col min="10" max="16384" width="9" style="1"/>
+    <col min="1" max="5" width="9" style="1"/>
+    <col min="6" max="6" width="9.75" style="1" customWidth="1"/>
+    <col min="7" max="7" width="12.625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="22.375" style="1" customWidth="1"/>
+    <col min="9" max="9" width="17.75" style="1" customWidth="1"/>
+    <col min="10" max="10" width="18.25" style="1" customWidth="1"/>
+    <col min="11" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" customHeight="1" spans="3:13">
-      <c r="J1" s="1" t="s">
+    <row r="1" customHeight="1" spans="3:14">
+      <c r="K1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" customHeight="1" spans="3:13">
-      <c r="J2" s="1" t="s">
+    <row r="2" customHeight="1" spans="3:14">
+      <c r="K2" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:13">
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:14">
       <c r="C3" s="3" t="s">
         <v>1</v>
       </c>
@@ -1245,8 +1278,11 @@
       <c r="I3" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:13">
+      <c r="J3" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:14">
       <c r="C4" s="3" t="s">
         <v>1</v>
       </c>
@@ -1268,16 +1304,19 @@
       <c r="I4" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:13">
+      <c r="J4" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:14">
       <c r="C5" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F5" s="3" t="s">
         <v>9</v>
@@ -1289,261 +1328,294 @@
         <v>11</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="6" s="2" customFormat="1" customHeight="1" spans="3:13">
+        <v>12</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" s="2" customFormat="1" customHeight="1" spans="3:14">
       <c r="C6" s="2">
         <v>1</v>
       </c>
       <c r="D6" s="2">
         <v>1</v>
       </c>
-      <c r="E6" s="4">
+      <c r="E6" s="2">
+        <v>1</v>
+      </c>
+      <c r="F6" s="4">
         <v>61000001</v>
       </c>
-      <c r="F6" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G6" s="6" t="s">
+      <c r="G6" s="1" t="s">
         <v>13</v>
       </c>
       <c r="H6" s="6" t="s">
         <v>14</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="M6" s="4"/>
-    </row>
-    <row r="7" s="2" customFormat="1" customHeight="1" spans="3:13">
+        <v>15</v>
+      </c>
+      <c r="J6" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="N6" s="4"/>
+    </row>
+    <row r="7" s="2" customFormat="1" customHeight="1" spans="3:14">
       <c r="C7" s="2">
         <v>2</v>
       </c>
       <c r="D7" s="2">
         <v>1</v>
       </c>
-      <c r="E7" s="4">
+      <c r="E7" s="2">
+        <v>1</v>
+      </c>
+      <c r="F7" s="4">
         <v>61000002</v>
       </c>
-      <c r="F7" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="G7" s="6" t="s">
+      <c r="G7" s="1" t="s">
         <v>16</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="M7" s="4"/>
-    </row>
-    <row r="8" s="1" customFormat="1" customHeight="1" spans="3:13">
+        <v>15</v>
+      </c>
+      <c r="J7" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="N7" s="4"/>
+    </row>
+    <row r="8" s="1" customFormat="1" customHeight="1" spans="3:14">
       <c r="C8" s="1">
         <v>3</v>
       </c>
       <c r="D8" s="2">
         <v>1</v>
       </c>
-      <c r="E8" s="4">
+      <c r="E8" s="2">
+        <v>1</v>
+      </c>
+      <c r="F8" s="4">
         <v>61000003</v>
       </c>
-      <c r="F8" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G8" s="6" t="s">
+      <c r="G8" s="1" t="s">
         <v>18</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="L8" s="2"/>
-      <c r="M8" s="4"/>
-    </row>
-    <row r="9" s="1" customFormat="1" ht="20" customHeight="1" spans="3:13">
+        <v>15</v>
+      </c>
+      <c r="J8" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="M8" s="2"/>
+      <c r="N8" s="4"/>
+    </row>
+    <row r="9" s="1" customFormat="1" ht="20" customHeight="1" spans="3:14">
       <c r="C9" s="1">
         <v>4</v>
       </c>
       <c r="D9" s="2">
         <v>1</v>
       </c>
-      <c r="E9" s="4">
+      <c r="E9" s="2">
+        <v>1</v>
+      </c>
+      <c r="F9" s="4">
         <v>61000004</v>
       </c>
-      <c r="F9" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="G9" s="6" t="s">
+      <c r="G9" s="1" t="s">
         <v>20</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="L9" s="2"/>
-      <c r="M9" s="4"/>
-    </row>
-    <row r="10" s="1" customFormat="1" customHeight="1" spans="3:13">
+        <v>15</v>
+      </c>
+      <c r="J9" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="M9" s="2"/>
+      <c r="N9" s="4"/>
+    </row>
+    <row r="10" s="1" customFormat="1" customHeight="1" spans="3:14">
       <c r="C10" s="1">
         <v>5</v>
       </c>
       <c r="D10" s="2">
         <v>1</v>
       </c>
-      <c r="E10" s="4">
+      <c r="E10" s="2">
+        <v>1</v>
+      </c>
+      <c r="F10" s="4">
         <v>61000005</v>
       </c>
-      <c r="F10" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="G10" s="6" t="s">
+      <c r="G10" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="L10" s="2"/>
-      <c r="M10" s="4"/>
-    </row>
-    <row r="11" s="1" customFormat="1" customHeight="1" spans="3:13">
+        <v>15</v>
+      </c>
+      <c r="J10" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="M10" s="2"/>
+      <c r="N10" s="4"/>
+    </row>
+    <row r="11" s="1" customFormat="1" customHeight="1" spans="3:14">
       <c r="C11" s="1">
         <v>6</v>
       </c>
       <c r="D11" s="2">
         <v>1</v>
       </c>
-      <c r="E11" s="4">
+      <c r="E11" s="2">
+        <v>1</v>
+      </c>
+      <c r="F11" s="4">
         <v>61000006</v>
       </c>
-      <c r="F11" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G11" s="6" t="s">
+      <c r="G11" s="1" t="s">
         <v>24</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="L11" s="2"/>
-      <c r="M11" s="4"/>
-    </row>
-    <row r="12" customHeight="1" spans="3:13">
+        <v>15</v>
+      </c>
+      <c r="J11" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="M11" s="2"/>
+      <c r="N11" s="4"/>
+    </row>
+    <row r="12" customHeight="1" spans="3:14">
       <c r="C12" s="1">
         <v>7</v>
       </c>
       <c r="D12" s="2">
         <v>1</v>
       </c>
-      <c r="E12" s="4">
+      <c r="E12" s="2">
+        <v>1</v>
+      </c>
+      <c r="F12" s="4">
         <v>61000007</v>
       </c>
-      <c r="F12" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G12" s="6" t="s">
+      <c r="G12" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="L12" s="2"/>
-      <c r="M12" s="4"/>
-    </row>
-    <row r="13" customHeight="1" spans="3:13">
+        <v>15</v>
+      </c>
+      <c r="J12" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="M12" s="2"/>
+      <c r="N12" s="4"/>
+    </row>
+    <row r="13" customHeight="1" spans="3:14">
       <c r="C13" s="1">
         <v>8</v>
       </c>
       <c r="D13" s="2">
         <v>1</v>
       </c>
-      <c r="E13" s="4">
+      <c r="E13" s="2">
+        <v>1</v>
+      </c>
+      <c r="F13" s="4">
         <v>61000008</v>
       </c>
-      <c r="F13" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="G13" s="6" t="s">
+      <c r="G13" s="5" t="s">
         <v>28</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="I13" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="L13" s="2"/>
-      <c r="M13" s="4"/>
-    </row>
-    <row r="14" customHeight="1" spans="3:13">
+        <v>15</v>
+      </c>
+      <c r="J13" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="M13" s="2"/>
+      <c r="N13" s="4"/>
+    </row>
+    <row r="14" customHeight="1" spans="3:14">
       <c r="D14" s="2"/>
-      <c r="E14" s="4"/>
-      <c r="G14" s="2"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="4"/>
       <c r="H14" s="2"/>
       <c r="I14" s="2"/>
-      <c r="L14" s="2"/>
-      <c r="M14" s="4"/>
-    </row>
-    <row r="15" customHeight="1" spans="3:13">
+      <c r="J14" s="2"/>
+      <c r="M14" s="2"/>
+      <c r="N14" s="4"/>
+    </row>
+    <row r="15" customHeight="1" spans="3:14">
       <c r="D15" s="2"/>
-      <c r="E15" s="4"/>
-      <c r="G15" s="2"/>
+      <c r="E15" s="2"/>
+      <c r="F15" s="4"/>
       <c r="H15" s="2"/>
       <c r="I15" s="2"/>
-      <c r="L15" s="2"/>
-      <c r="M15" s="4"/>
-    </row>
-    <row r="16" customFormat="1" customHeight="1" spans="3:13">
+      <c r="J15" s="2"/>
+      <c r="M15" s="2"/>
+      <c r="N15" s="4"/>
+    </row>
+    <row r="16" customFormat="1" customHeight="1" spans="3:14">
       <c r="C16" s="1"/>
       <c r="D16" s="1"/>
-      <c r="E16" s="4"/>
-      <c r="F16" s="1"/>
+      <c r="E16" s="1"/>
+      <c r="F16" s="4"/>
       <c r="G16" s="1"/>
       <c r="H16" s="1"/>
       <c r="I16" s="1"/>
-      <c r="L16" s="2"/>
-      <c r="M16" s="4"/>
-    </row>
-    <row r="17" s="2" customFormat="1" customHeight="1" spans="1:13">
+      <c r="J16" s="1"/>
+      <c r="M16" s="2"/>
+      <c r="N16" s="4"/>
+    </row>
+    <row r="17" s="2" customFormat="1" customHeight="1" spans="1:14">
       <c r="C17" s="2">
         <v>9</v>
       </c>
       <c r="D17" s="2">
         <v>2</v>
       </c>
-      <c r="E17" s="4">
+      <c r="E17" s="2">
+        <v>1</v>
+      </c>
+      <c r="F17" s="4">
         <v>61000009</v>
       </c>
-      <c r="F17" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="G17" s="6" t="s">
-        <v>13</v>
+      <c r="G17" s="1" t="s">
+        <v>30</v>
       </c>
       <c r="H17" s="6" t="s">
         <v>14</v>
       </c>
       <c r="I17" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="M17" s="4"/>
-    </row>
-    <row r="18" customHeight="1" spans="1:13">
+        <v>15</v>
+      </c>
+      <c r="J17" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="N17" s="4"/>
+    </row>
+    <row r="18" customHeight="1" spans="1:14">
       <c r="A18" s="2"/>
       <c r="B18" s="2"/>
       <c r="C18" s="2">
@@ -1552,73 +1624,82 @@
       <c r="D18" s="2">
         <v>2</v>
       </c>
-      <c r="E18" s="4">
+      <c r="E18" s="2">
+        <v>1</v>
+      </c>
+      <c r="F18" s="4">
         <v>61000010</v>
       </c>
-      <c r="F18" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="G18" s="6" t="s">
-        <v>16</v>
+      <c r="G18" s="1" t="s">
+        <v>31</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I18" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="L18" s="2"/>
-      <c r="M18" s="4"/>
-    </row>
-    <row r="19" s="2" customFormat="1" customHeight="1" spans="1:13">
+        <v>15</v>
+      </c>
+      <c r="J18" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="M18" s="2"/>
+      <c r="N18" s="4"/>
+    </row>
+    <row r="19" s="2" customFormat="1" customHeight="1" spans="1:14">
       <c r="C19" s="2">
         <v>11</v>
       </c>
       <c r="D19" s="2">
         <v>2</v>
       </c>
-      <c r="E19" s="4">
+      <c r="E19" s="2">
+        <v>1</v>
+      </c>
+      <c r="F19" s="4">
         <v>61000011</v>
       </c>
-      <c r="F19" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="G19" s="6" t="s">
-        <v>18</v>
+      <c r="G19" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="I19" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="M19" s="4"/>
-    </row>
-    <row r="20" s="2" customFormat="1" customHeight="1" spans="1:13">
+        <v>15</v>
+      </c>
+      <c r="J19" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="N19" s="4"/>
+    </row>
+    <row r="20" s="2" customFormat="1" customHeight="1" spans="1:14">
       <c r="C20" s="2">
         <v>12</v>
       </c>
       <c r="D20" s="2">
         <v>2</v>
       </c>
-      <c r="E20" s="4">
+      <c r="E20" s="2">
+        <v>1</v>
+      </c>
+      <c r="F20" s="4">
         <v>61000012</v>
       </c>
-      <c r="F20" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="G20" s="6" t="s">
-        <v>20</v>
+      <c r="G20" s="1" t="s">
+        <v>33</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="I20" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="M20" s="4"/>
-    </row>
-    <row r="21" s="1" customFormat="1" customHeight="1" spans="1:13">
+        <v>15</v>
+      </c>
+      <c r="J20" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="N20" s="4"/>
+    </row>
+    <row r="21" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="A21" s="2"/>
       <c r="B21" s="2"/>
       <c r="C21" s="2">
@@ -1627,25 +1708,28 @@
       <c r="D21" s="2">
         <v>2</v>
       </c>
-      <c r="E21" s="4">
+      <c r="E21" s="2">
+        <v>1</v>
+      </c>
+      <c r="F21" s="4">
         <v>61000013</v>
       </c>
-      <c r="F21" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="G21" s="6" t="s">
-        <v>22</v>
+      <c r="G21" s="1" t="s">
+        <v>34</v>
       </c>
       <c r="H21" s="6" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="I21" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="L21" s="2"/>
-      <c r="M21" s="4"/>
-    </row>
-    <row r="22" customHeight="1" spans="1:13">
+        <v>15</v>
+      </c>
+      <c r="J21" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="M21" s="2"/>
+      <c r="N21" s="4"/>
+    </row>
+    <row r="22" customHeight="1" spans="1:14">
       <c r="A22" s="2"/>
       <c r="B22" s="2"/>
       <c r="C22" s="2">
@@ -1654,51 +1738,57 @@
       <c r="D22" s="2">
         <v>2</v>
       </c>
-      <c r="E22" s="4">
+      <c r="E22" s="2">
+        <v>1</v>
+      </c>
+      <c r="F22" s="4">
         <v>61000014</v>
       </c>
-      <c r="F22" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="G22" s="6" t="s">
-        <v>24</v>
+      <c r="G22" s="1" t="s">
+        <v>35</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="I22" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="L22" s="2"/>
-      <c r="M22" s="4"/>
-    </row>
-    <row r="23" s="2" customFormat="1" customHeight="1" spans="1:13">
+        <v>15</v>
+      </c>
+      <c r="J22" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="M22" s="2"/>
+      <c r="N22" s="4"/>
+    </row>
+    <row r="23" s="2" customFormat="1" customHeight="1" spans="1:14">
       <c r="C23" s="2">
         <v>15</v>
       </c>
       <c r="D23" s="2">
         <v>2</v>
       </c>
-      <c r="E23" s="4">
+      <c r="E23" s="2">
+        <v>1</v>
+      </c>
+      <c r="F23" s="4">
         <v>61000015</v>
       </c>
-      <c r="F23" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="G23" s="6" t="s">
-        <v>26</v>
+      <c r="G23" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="H23" s="6" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="I23" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="J23" s="1"/>
+        <v>15</v>
+      </c>
+      <c r="J23" s="6" t="s">
+        <v>15</v>
+      </c>
       <c r="K23" s="1"/>
-      <c r="M23" s="4"/>
-    </row>
-    <row r="24" customHeight="1" spans="1:13">
+      <c r="L23" s="1"/>
+      <c r="N23" s="4"/>
+    </row>
+    <row r="24" customHeight="1" spans="1:14">
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
       <c r="C24" s="2">
@@ -1707,655 +1797,932 @@
       <c r="D24" s="2">
         <v>2</v>
       </c>
-      <c r="E24" s="4">
+      <c r="E24" s="2">
+        <v>1</v>
+      </c>
+      <c r="F24" s="4">
         <v>61000016</v>
       </c>
-      <c r="F24" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="G24" s="6" t="s">
-        <v>28</v>
+      <c r="G24" s="5" t="s">
+        <v>37</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="I24" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="L24" s="2"/>
-      <c r="M24" s="4"/>
-    </row>
-    <row r="25" customHeight="1" spans="1:13">
-      <c r="L25" s="2"/>
-      <c r="M25" s="4"/>
-    </row>
-    <row r="26" customHeight="1" spans="1:13">
+        <v>15</v>
+      </c>
+      <c r="J24" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="M24" s="2"/>
+      <c r="N24" s="4"/>
+    </row>
+    <row r="25" customHeight="1" spans="1:14">
+      <c r="M25" s="2"/>
+      <c r="N25" s="4"/>
+    </row>
+    <row r="26" customHeight="1" spans="1:14">
       <c r="C26" s="2">
         <v>17</v>
       </c>
       <c r="D26" s="2">
         <v>3</v>
       </c>
-      <c r="E26" s="4">
+      <c r="E26" s="2">
+        <v>1</v>
+      </c>
+      <c r="F26" s="4">
         <v>61000017</v>
       </c>
-      <c r="F26" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="G26" s="6" t="s">
+      <c r="G26" s="1" t="s">
         <v>38</v>
       </c>
       <c r="H26" s="6" t="s">
         <v>39</v>
       </c>
       <c r="I26" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="L26" s="2"/>
-      <c r="M26" s="4"/>
-    </row>
-    <row r="27" customHeight="1" spans="1:13">
+        <v>40</v>
+      </c>
+      <c r="J26" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="M26" s="2"/>
+      <c r="N26" s="4"/>
+    </row>
+    <row r="27" customHeight="1" spans="1:14">
       <c r="C27" s="2">
         <v>18</v>
       </c>
       <c r="D27" s="2">
         <v>3</v>
       </c>
-      <c r="E27" s="4">
+      <c r="E27" s="2">
+        <v>1</v>
+      </c>
+      <c r="F27" s="4">
         <v>61000018</v>
       </c>
-      <c r="F27" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="G27" s="6" t="s">
-        <v>38</v>
+      <c r="G27" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="H27" s="6" t="s">
         <v>39</v>
       </c>
       <c r="I27" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="L27" s="2"/>
-      <c r="M27" s="4"/>
-    </row>
-    <row r="28" customHeight="1" spans="1:13">
+        <v>40</v>
+      </c>
+      <c r="J27" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="M27" s="2"/>
+      <c r="N27" s="4"/>
+    </row>
+    <row r="28" customHeight="1" spans="1:14">
       <c r="C28" s="2">
         <v>19</v>
       </c>
       <c r="D28" s="2">
         <v>3</v>
       </c>
-      <c r="E28" s="4">
+      <c r="E28" s="2">
+        <v>1</v>
+      </c>
+      <c r="F28" s="4">
         <v>61000019</v>
       </c>
-      <c r="F28" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="G28" s="6" t="s">
-        <v>38</v>
+      <c r="G28" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="H28" s="6" t="s">
         <v>39</v>
       </c>
       <c r="I28" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="L28" s="2"/>
-      <c r="M28" s="4"/>
-    </row>
-    <row r="29" customHeight="1" spans="1:13">
+        <v>40</v>
+      </c>
+      <c r="J28" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="M28" s="2"/>
+      <c r="N28" s="4"/>
+    </row>
+    <row r="29" customHeight="1" spans="1:14">
       <c r="C29" s="2">
         <v>20</v>
       </c>
       <c r="D29" s="2">
         <v>3</v>
       </c>
-      <c r="E29" s="4">
+      <c r="E29" s="2">
+        <v>1</v>
+      </c>
+      <c r="F29" s="4">
         <v>61000020</v>
       </c>
-      <c r="F29" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="G29" s="6" t="s">
-        <v>38</v>
+      <c r="G29" s="1" t="s">
+        <v>43</v>
       </c>
       <c r="H29" s="6" t="s">
         <v>39</v>
       </c>
       <c r="I29" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="L29" s="2"/>
-      <c r="M29" s="4"/>
-    </row>
-    <row r="30" customHeight="1" spans="1:13">
+        <v>40</v>
+      </c>
+      <c r="J29" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="M29" s="2"/>
+      <c r="N29" s="4"/>
+    </row>
+    <row r="30" customHeight="1" spans="1:14">
       <c r="C30" s="2">
         <v>21</v>
       </c>
       <c r="D30" s="2">
         <v>3</v>
       </c>
-      <c r="E30" s="4">
+      <c r="E30" s="2">
+        <v>1</v>
+      </c>
+      <c r="F30" s="4">
         <v>61000021</v>
       </c>
-      <c r="F30" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="G30" s="6" t="s">
-        <v>38</v>
+      <c r="G30" s="1" t="s">
+        <v>44</v>
       </c>
       <c r="H30" s="6" t="s">
         <v>39</v>
       </c>
       <c r="I30" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="L30" s="2"/>
-      <c r="M30" s="4"/>
-    </row>
-    <row r="31" customHeight="1" spans="1:13">
+        <v>40</v>
+      </c>
+      <c r="J30" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="M30" s="2"/>
+      <c r="N30" s="4"/>
+    </row>
+    <row r="31" customHeight="1" spans="1:14">
       <c r="C31" s="2">
         <v>22</v>
       </c>
       <c r="D31" s="2">
         <v>3</v>
       </c>
-      <c r="E31" s="4">
+      <c r="E31" s="2">
+        <v>1</v>
+      </c>
+      <c r="F31" s="4">
         <v>61000022</v>
       </c>
-      <c r="F31" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="G31" s="6" t="s">
-        <v>38</v>
+      <c r="G31" s="1" t="s">
+        <v>45</v>
       </c>
       <c r="H31" s="6" t="s">
         <v>39</v>
       </c>
       <c r="I31" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="L31" s="2"/>
-      <c r="M31" s="4"/>
-    </row>
-    <row r="32" customHeight="1" spans="1:13">
+        <v>40</v>
+      </c>
+      <c r="J31" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="M31" s="2"/>
+      <c r="N31" s="4"/>
+    </row>
+    <row r="32" customHeight="1" spans="1:14">
       <c r="C32" s="2">
         <v>23</v>
       </c>
       <c r="D32" s="2">
         <v>3</v>
       </c>
-      <c r="E32" s="4">
+      <c r="E32" s="2">
+        <v>1</v>
+      </c>
+      <c r="F32" s="4">
         <v>61000023</v>
       </c>
-      <c r="F32" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="G32" s="6" t="s">
-        <v>38</v>
+      <c r="G32" s="1" t="s">
+        <v>46</v>
       </c>
       <c r="H32" s="6" t="s">
         <v>39</v>
       </c>
       <c r="I32" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="L32" s="2"/>
-      <c r="M32" s="4"/>
-    </row>
-    <row r="33" customHeight="1" spans="3:13">
+        <v>40</v>
+      </c>
+      <c r="J32" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="M32" s="2"/>
+      <c r="N32" s="4"/>
+    </row>
+    <row r="33" customHeight="1" spans="3:14">
       <c r="C33" s="2">
         <v>24</v>
       </c>
       <c r="D33" s="2">
         <v>3</v>
       </c>
-      <c r="E33" s="4">
+      <c r="E33" s="2">
+        <v>1</v>
+      </c>
+      <c r="F33" s="4">
         <v>61000024</v>
       </c>
-      <c r="F33" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="G33" s="6" t="s">
-        <v>38</v>
+      <c r="G33" s="5" t="s">
+        <v>47</v>
       </c>
       <c r="H33" s="6" t="s">
         <v>39</v>
       </c>
       <c r="I33" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="L33" s="2"/>
-      <c r="M33" s="4"/>
-    </row>
-    <row r="34" customHeight="1" spans="3:13">
-      <c r="L34" s="2"/>
-      <c r="M34" s="4"/>
-    </row>
-    <row r="35" customHeight="1" spans="3:13">
+        <v>40</v>
+      </c>
+      <c r="J33" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="M33" s="2"/>
+      <c r="N33" s="4"/>
+    </row>
+    <row r="34" customHeight="1" spans="3:14">
+      <c r="M34" s="2"/>
+      <c r="N34" s="4"/>
+    </row>
+    <row r="35" customHeight="1" spans="3:14">
       <c r="C35" s="2">
         <v>25</v>
       </c>
       <c r="D35" s="2">
         <v>4</v>
       </c>
-      <c r="E35" s="4">
+      <c r="E35" s="2">
+        <v>1</v>
+      </c>
+      <c r="F35" s="4">
         <v>61000025</v>
       </c>
-      <c r="F35" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="G35" s="6" t="s">
+      <c r="G35" s="1" t="s">
         <v>48</v>
       </c>
       <c r="H35" s="6" t="s">
         <v>49</v>
       </c>
       <c r="I35" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="L35" s="2"/>
-      <c r="M35" s="4"/>
-    </row>
-    <row r="36" customHeight="1" spans="3:13">
+        <v>50</v>
+      </c>
+      <c r="J35" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="M35" s="2"/>
+      <c r="N35" s="4"/>
+    </row>
+    <row r="36" customHeight="1" spans="3:14">
       <c r="C36" s="2">
         <v>26</v>
       </c>
       <c r="D36" s="2">
         <v>4</v>
       </c>
-      <c r="E36" s="4">
+      <c r="E36" s="2">
+        <v>1</v>
+      </c>
+      <c r="F36" s="4">
         <v>61000026</v>
       </c>
-      <c r="F36" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="G36" s="6" t="s">
-        <v>48</v>
+      <c r="G36" s="1" t="s">
+        <v>51</v>
       </c>
       <c r="H36" s="6" t="s">
         <v>49</v>
       </c>
       <c r="I36" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="L36" s="2"/>
-      <c r="M36" s="4"/>
-    </row>
-    <row r="37" customHeight="1" spans="3:13">
+        <v>50</v>
+      </c>
+      <c r="J36" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="M36" s="2"/>
+      <c r="N36" s="4"/>
+    </row>
+    <row r="37" customHeight="1" spans="3:14">
       <c r="C37" s="2">
         <v>27</v>
       </c>
       <c r="D37" s="2">
         <v>4</v>
       </c>
-      <c r="E37" s="4">
+      <c r="E37" s="2">
+        <v>1</v>
+      </c>
+      <c r="F37" s="4">
         <v>61000027</v>
       </c>
-      <c r="F37" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="G37" s="6" t="s">
-        <v>48</v>
+      <c r="G37" s="1" t="s">
+        <v>52</v>
       </c>
       <c r="H37" s="6" t="s">
         <v>49</v>
       </c>
       <c r="I37" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="L37" s="2"/>
-      <c r="M37" s="4"/>
-    </row>
-    <row r="38" customHeight="1" spans="3:13">
+        <v>50</v>
+      </c>
+      <c r="J37" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="M37" s="2"/>
+      <c r="N37" s="4"/>
+    </row>
+    <row r="38" customHeight="1" spans="3:14">
       <c r="C38" s="2">
         <v>28</v>
       </c>
       <c r="D38" s="2">
         <v>4</v>
       </c>
-      <c r="E38" s="4">
+      <c r="E38" s="2">
+        <v>1</v>
+      </c>
+      <c r="F38" s="4">
         <v>61000028</v>
       </c>
-      <c r="F38" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="G38" s="6" t="s">
-        <v>48</v>
+      <c r="G38" s="1" t="s">
+        <v>53</v>
       </c>
       <c r="H38" s="6" t="s">
         <v>49</v>
       </c>
       <c r="I38" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="L38" s="2"/>
-      <c r="M38" s="4"/>
-    </row>
-    <row r="39" customHeight="1" spans="3:13">
+        <v>50</v>
+      </c>
+      <c r="J38" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="M38" s="2"/>
+      <c r="N38" s="4"/>
+    </row>
+    <row r="39" customHeight="1" spans="3:14">
       <c r="C39" s="2">
         <v>29</v>
       </c>
       <c r="D39" s="2">
         <v>4</v>
       </c>
-      <c r="E39" s="4">
+      <c r="E39" s="2">
+        <v>1</v>
+      </c>
+      <c r="F39" s="4">
         <v>61000029</v>
       </c>
-      <c r="F39" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="G39" s="6" t="s">
-        <v>48</v>
+      <c r="G39" s="1" t="s">
+        <v>54</v>
       </c>
       <c r="H39" s="6" t="s">
         <v>49</v>
       </c>
       <c r="I39" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="L39" s="2"/>
-      <c r="M39" s="4"/>
-    </row>
-    <row r="40" customHeight="1" spans="3:13">
+        <v>50</v>
+      </c>
+      <c r="J39" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="M39" s="2"/>
+      <c r="N39" s="4"/>
+    </row>
+    <row r="40" customHeight="1" spans="3:14">
       <c r="C40" s="2">
         <v>30</v>
       </c>
       <c r="D40" s="2">
         <v>4</v>
       </c>
-      <c r="E40" s="4">
+      <c r="E40" s="2">
+        <v>1</v>
+      </c>
+      <c r="F40" s="4">
         <v>61000030</v>
       </c>
-      <c r="F40" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="G40" s="6" t="s">
-        <v>48</v>
+      <c r="G40" s="1" t="s">
+        <v>55</v>
       </c>
       <c r="H40" s="6" t="s">
         <v>49</v>
       </c>
       <c r="I40" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="L40" s="2"/>
-      <c r="M40" s="4"/>
-    </row>
-    <row r="41" customHeight="1" spans="3:13">
+        <v>50</v>
+      </c>
+      <c r="J40" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="M40" s="2"/>
+      <c r="N40" s="4"/>
+    </row>
+    <row r="41" customHeight="1" spans="3:14">
       <c r="C41" s="2">
         <v>31</v>
       </c>
       <c r="D41" s="2">
         <v>4</v>
       </c>
-      <c r="E41" s="4">
+      <c r="E41" s="2">
+        <v>1</v>
+      </c>
+      <c r="F41" s="4">
         <v>61000031</v>
       </c>
-      <c r="F41" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="G41" s="6" t="s">
-        <v>48</v>
+      <c r="G41" s="1" t="s">
+        <v>56</v>
       </c>
       <c r="H41" s="6" t="s">
         <v>49</v>
       </c>
       <c r="I41" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="L41" s="2"/>
-      <c r="M41" s="4"/>
-    </row>
-    <row r="42" customHeight="1" spans="3:13">
+        <v>50</v>
+      </c>
+      <c r="J41" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="M41" s="2"/>
+      <c r="N41" s="4"/>
+    </row>
+    <row r="42" customHeight="1" spans="3:14">
       <c r="C42" s="2">
         <v>32</v>
       </c>
       <c r="D42" s="2">
         <v>4</v>
       </c>
-      <c r="E42" s="4">
+      <c r="E42" s="2">
+        <v>1</v>
+      </c>
+      <c r="F42" s="4">
         <v>61000032</v>
       </c>
-      <c r="F42" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="G42" s="6" t="s">
-        <v>48</v>
+      <c r="G42" s="5" t="s">
+        <v>57</v>
       </c>
       <c r="H42" s="6" t="s">
         <v>49</v>
       </c>
       <c r="I42" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="L42" s="2"/>
-      <c r="M42" s="4"/>
-    </row>
-    <row r="43" customHeight="1" spans="3:13">
-      <c r="L43" s="2"/>
-      <c r="M43" s="4"/>
-    </row>
-    <row r="44" customHeight="1" spans="3:13">
+        <v>50</v>
+      </c>
+      <c r="J42" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="M42" s="2"/>
+      <c r="N42" s="4"/>
+    </row>
+    <row r="43" customHeight="1" spans="3:14">
+      <c r="M43" s="2"/>
+      <c r="N43" s="4"/>
+    </row>
+    <row r="44" customHeight="1" spans="3:14">
       <c r="C44" s="2">
         <v>33</v>
       </c>
       <c r="D44" s="2">
         <v>5</v>
       </c>
-      <c r="E44" s="4">
+      <c r="E44" s="2">
+        <v>1</v>
+      </c>
+      <c r="F44" s="4">
         <v>61000033</v>
       </c>
-      <c r="F44" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="G44" s="6" t="s">
+      <c r="G44" s="1" t="s">
         <v>58</v>
       </c>
       <c r="H44" s="6" t="s">
         <v>59</v>
       </c>
       <c r="I44" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="L44" s="2"/>
-      <c r="M44" s="4"/>
-    </row>
-    <row r="45" customHeight="1" spans="3:13">
+        <v>60</v>
+      </c>
+      <c r="J44" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="M44" s="2"/>
+      <c r="N44" s="4"/>
+    </row>
+    <row r="45" customHeight="1" spans="3:14">
       <c r="C45" s="2">
         <v>34</v>
       </c>
       <c r="D45" s="2">
         <v>5</v>
       </c>
-      <c r="E45" s="4">
+      <c r="E45" s="2">
+        <v>1</v>
+      </c>
+      <c r="F45" s="4">
         <v>61000034</v>
       </c>
-      <c r="F45" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="G45" s="6" t="s">
-        <v>58</v>
+      <c r="G45" s="1" t="s">
+        <v>61</v>
       </c>
       <c r="H45" s="6" t="s">
         <v>59</v>
       </c>
       <c r="I45" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="L45" s="2"/>
-      <c r="M45" s="4"/>
-    </row>
-    <row r="46" customHeight="1" spans="3:13">
+        <v>60</v>
+      </c>
+      <c r="J45" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="M45" s="2"/>
+      <c r="N45" s="4"/>
+    </row>
+    <row r="46" customHeight="1" spans="3:14">
       <c r="C46" s="2">
         <v>35</v>
       </c>
       <c r="D46" s="2">
         <v>5</v>
       </c>
-      <c r="E46" s="4">
+      <c r="E46" s="2">
+        <v>1</v>
+      </c>
+      <c r="F46" s="4">
         <v>61000035</v>
       </c>
-      <c r="F46" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="G46" s="6" t="s">
-        <v>58</v>
+      <c r="G46" s="1" t="s">
+        <v>62</v>
       </c>
       <c r="H46" s="6" t="s">
         <v>59</v>
       </c>
       <c r="I46" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="L46" s="2"/>
-      <c r="M46" s="4"/>
-    </row>
-    <row r="47" customHeight="1" spans="3:13">
+        <v>60</v>
+      </c>
+      <c r="J46" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="M46" s="2"/>
+      <c r="N46" s="4"/>
+    </row>
+    <row r="47" customHeight="1" spans="3:14">
       <c r="C47" s="2">
         <v>36</v>
       </c>
       <c r="D47" s="2">
         <v>5</v>
       </c>
-      <c r="E47" s="4">
+      <c r="E47" s="2">
+        <v>1</v>
+      </c>
+      <c r="F47" s="4">
         <v>61000036</v>
       </c>
-      <c r="F47" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="G47" s="6" t="s">
-        <v>58</v>
+      <c r="G47" s="1" t="s">
+        <v>63</v>
       </c>
       <c r="H47" s="6" t="s">
         <v>59</v>
       </c>
       <c r="I47" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="L47" s="2"/>
-      <c r="M47" s="4"/>
-    </row>
-    <row r="48" customHeight="1" spans="3:13">
+        <v>60</v>
+      </c>
+      <c r="J47" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="M47" s="2"/>
+      <c r="N47" s="4"/>
+    </row>
+    <row r="48" customHeight="1" spans="3:14">
       <c r="C48" s="2">
         <v>37</v>
       </c>
       <c r="D48" s="2">
         <v>5</v>
       </c>
-      <c r="E48" s="4">
+      <c r="E48" s="2">
+        <v>1</v>
+      </c>
+      <c r="F48" s="4">
         <v>61000037</v>
       </c>
-      <c r="F48" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="G48" s="6" t="s">
-        <v>58</v>
+      <c r="G48" s="1" t="s">
+        <v>64</v>
       </c>
       <c r="H48" s="6" t="s">
         <v>59</v>
       </c>
       <c r="I48" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="L48" s="2"/>
-      <c r="M48" s="4"/>
-    </row>
-    <row r="49" customHeight="1" spans="3:13">
+        <v>60</v>
+      </c>
+      <c r="J48" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="M48" s="2"/>
+      <c r="N48" s="4"/>
+    </row>
+    <row r="49" customHeight="1" spans="3:14">
       <c r="C49" s="2">
         <v>38</v>
       </c>
       <c r="D49" s="2">
         <v>5</v>
       </c>
-      <c r="E49" s="4">
+      <c r="E49" s="2">
+        <v>1</v>
+      </c>
+      <c r="F49" s="4">
         <v>61000038</v>
       </c>
-      <c r="F49" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="G49" s="6" t="s">
-        <v>58</v>
+      <c r="G49" s="1" t="s">
+        <v>65</v>
       </c>
       <c r="H49" s="6" t="s">
         <v>59</v>
       </c>
       <c r="I49" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="L49" s="2"/>
-      <c r="M49" s="4"/>
-    </row>
-    <row r="50" customHeight="1" spans="3:13">
+        <v>60</v>
+      </c>
+      <c r="J49" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="M49" s="2"/>
+      <c r="N49" s="4"/>
+    </row>
+    <row r="50" customHeight="1" spans="3:14">
       <c r="C50" s="2">
         <v>39</v>
       </c>
       <c r="D50" s="2">
         <v>5</v>
       </c>
-      <c r="E50" s="4">
+      <c r="E50" s="2">
+        <v>1</v>
+      </c>
+      <c r="F50" s="4">
         <v>61000039</v>
       </c>
-      <c r="F50" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="G50" s="6" t="s">
-        <v>58</v>
+      <c r="G50" s="1" t="s">
+        <v>66</v>
       </c>
       <c r="H50" s="6" t="s">
         <v>59</v>
       </c>
       <c r="I50" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="L50" s="2"/>
-      <c r="M50" s="4"/>
-    </row>
-    <row r="51" customHeight="1" spans="3:13">
+        <v>60</v>
+      </c>
+      <c r="J50" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="M50" s="2"/>
+      <c r="N50" s="4"/>
+    </row>
+    <row r="51" customHeight="1" spans="3:14">
       <c r="C51" s="2">
         <v>40</v>
       </c>
       <c r="D51" s="2">
         <v>5</v>
       </c>
-      <c r="E51" s="4">
+      <c r="E51" s="2">
+        <v>1</v>
+      </c>
+      <c r="F51" s="4">
         <v>61000040</v>
       </c>
-      <c r="F51" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="G51" s="6" t="s">
-        <v>58</v>
+      <c r="G51" s="5" t="s">
+        <v>67</v>
       </c>
       <c r="H51" s="6" t="s">
         <v>59</v>
       </c>
       <c r="I51" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="L51" s="2"/>
-      <c r="M51" s="4"/>
-    </row>
-    <row r="52" customHeight="1" spans="3:13">
-      <c r="L52" s="2"/>
-      <c r="M52" s="4"/>
-    </row>
-    <row r="53" customHeight="1" spans="3:13">
-      <c r="L53" s="2"/>
-      <c r="M53" s="4"/>
-    </row>
-    <row r="54" customHeight="1" spans="3:13">
-      <c r="L54" s="2"/>
-      <c r="M54" s="4"/>
-    </row>
-    <row r="55" customHeight="1" spans="3:13">
-      <c r="L55" s="2"/>
-      <c r="M55" s="4"/>
+        <v>60</v>
+      </c>
+      <c r="J51" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="M51" s="2"/>
+      <c r="N51" s="4"/>
+    </row>
+    <row r="52" customHeight="1" spans="3:14">
+      <c r="M52" s="2"/>
+      <c r="N52" s="4"/>
+    </row>
+    <row r="53" customHeight="1" spans="3:14">
+      <c r="C53" s="2">
+        <v>41</v>
+      </c>
+      <c r="D53" s="2">
+        <v>6</v>
+      </c>
+      <c r="E53" s="2">
+        <v>2</v>
+      </c>
+      <c r="F53" s="4">
+        <v>61000041</v>
+      </c>
+      <c r="G53" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="H53" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="I53" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="J53" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="M53" s="2"/>
+      <c r="N53" s="4"/>
+    </row>
+    <row r="54" customHeight="1" spans="3:14">
+      <c r="C54" s="2">
+        <v>42</v>
+      </c>
+      <c r="D54" s="2">
+        <v>6</v>
+      </c>
+      <c r="E54" s="2">
+        <v>2</v>
+      </c>
+      <c r="F54" s="4">
+        <v>61000042</v>
+      </c>
+      <c r="G54" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="H54" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="I54" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="J54" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="M54" s="2"/>
+      <c r="N54" s="4"/>
+    </row>
+    <row r="55" customHeight="1" spans="3:14">
+      <c r="C55" s="2">
+        <v>43</v>
+      </c>
+      <c r="D55" s="2">
+        <v>6</v>
+      </c>
+      <c r="E55" s="2">
+        <v>2</v>
+      </c>
+      <c r="F55" s="4">
+        <v>61000043</v>
+      </c>
+      <c r="G55" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="H55" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="I55" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="J55" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="M55" s="2"/>
+      <c r="N55" s="4"/>
+    </row>
+    <row r="56" customHeight="1" spans="3:14">
+      <c r="C56" s="2">
+        <v>44</v>
+      </c>
+      <c r="D56" s="2">
+        <v>6</v>
+      </c>
+      <c r="E56" s="2">
+        <v>2</v>
+      </c>
+      <c r="F56" s="4">
+        <v>61000044</v>
+      </c>
+      <c r="G56" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H56" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="I56" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="J56" s="6" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="57" customHeight="1" spans="3:14">
+      <c r="C57" s="2">
+        <v>45</v>
+      </c>
+      <c r="D57" s="2">
+        <v>6</v>
+      </c>
+      <c r="E57" s="2">
+        <v>2</v>
+      </c>
+      <c r="F57" s="4">
+        <v>61000045</v>
+      </c>
+      <c r="G57" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="H57" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="I57" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="J57" s="6" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="58" customHeight="1" spans="3:14">
+      <c r="C58" s="2">
+        <v>46</v>
+      </c>
+      <c r="D58" s="2">
+        <v>6</v>
+      </c>
+      <c r="E58" s="2">
+        <v>2</v>
+      </c>
+      <c r="F58" s="4">
+        <v>61000046</v>
+      </c>
+      <c r="G58" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="H58" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="I58" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="J58" s="6" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="59" customHeight="1" spans="3:14">
+      <c r="C59" s="2">
+        <v>47</v>
+      </c>
+      <c r="D59" s="2">
+        <v>6</v>
+      </c>
+      <c r="E59" s="2">
+        <v>2</v>
+      </c>
+      <c r="F59" s="4">
+        <v>61000047</v>
+      </c>
+      <c r="G59" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="H59" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="I59" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="J59" s="6" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="60" customHeight="1" spans="3:14">
+      <c r="C60" s="2">
+        <v>48</v>
+      </c>
+      <c r="D60" s="2">
+        <v>6</v>
+      </c>
+      <c r="E60" s="2">
+        <v>2</v>
+      </c>
+      <c r="F60" s="4">
+        <v>61000048</v>
+      </c>
+      <c r="G60" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="H60" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="I60" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="J60" s="6" t="s">
+        <v>70</v>
+      </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:F5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="E3 E4 E5 C3:D5 F3:G5" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/RelicConfig.xlsx
+++ b/Excel/RelicConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="86">
   <si>
     <t>#</t>
   </si>
@@ -261,6 +261,30 @@
   </si>
   <si>
     <t>极龙战靴</t>
+  </si>
+  <si>
+    <t>极虎神剑</t>
+  </si>
+  <si>
+    <t>极虎神甲</t>
+  </si>
+  <si>
+    <t>极虎面罩</t>
+  </si>
+  <si>
+    <t>极虎项链</t>
+  </si>
+  <si>
+    <t>极虎护腕</t>
+  </si>
+  <si>
+    <t>极虎护戒</t>
+  </si>
+  <si>
+    <t>极虎腰带</t>
+  </si>
+  <si>
+    <t>极虎战靴</t>
   </si>
 </sst>
 </file>
@@ -1234,7 +1258,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N60"/>
+  <dimension ref="A1:N69"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="5" width="9" style="1"/>
@@ -2720,9 +2744,217 @@
         <v>70</v>
       </c>
     </row>
+    <row r="62" customHeight="1" spans="3:14">
+      <c r="C62" s="2">
+        <v>49</v>
+      </c>
+      <c r="D62" s="2">
+        <v>6</v>
+      </c>
+      <c r="E62" s="2">
+        <v>2</v>
+      </c>
+      <c r="F62" s="4">
+        <v>61000049</v>
+      </c>
+      <c r="G62" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="H62" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="I62" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="J62" s="6" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="63" customHeight="1" spans="3:14">
+      <c r="C63" s="2">
+        <v>50</v>
+      </c>
+      <c r="D63" s="2">
+        <v>6</v>
+      </c>
+      <c r="E63" s="2">
+        <v>2</v>
+      </c>
+      <c r="F63" s="4">
+        <v>61000050</v>
+      </c>
+      <c r="G63" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="H63" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="I63" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="J63" s="6" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="64" customHeight="1" spans="3:14">
+      <c r="C64" s="2">
+        <v>51</v>
+      </c>
+      <c r="D64" s="2">
+        <v>6</v>
+      </c>
+      <c r="E64" s="2">
+        <v>2</v>
+      </c>
+      <c r="F64" s="4">
+        <v>61000051</v>
+      </c>
+      <c r="G64" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="H64" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="I64" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="J64" s="6" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="65" customHeight="1" spans="3:10">
+      <c r="C65" s="2">
+        <v>52</v>
+      </c>
+      <c r="D65" s="2">
+        <v>6</v>
+      </c>
+      <c r="E65" s="2">
+        <v>2</v>
+      </c>
+      <c r="F65" s="4">
+        <v>61000052</v>
+      </c>
+      <c r="G65" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="H65" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="I65" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="J65" s="6" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="66" customHeight="1" spans="3:10">
+      <c r="C66" s="2">
+        <v>53</v>
+      </c>
+      <c r="D66" s="2">
+        <v>6</v>
+      </c>
+      <c r="E66" s="2">
+        <v>2</v>
+      </c>
+      <c r="F66" s="4">
+        <v>61000053</v>
+      </c>
+      <c r="G66" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="H66" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="I66" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="J66" s="6" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="67" customHeight="1" spans="3:10">
+      <c r="C67" s="2">
+        <v>54</v>
+      </c>
+      <c r="D67" s="2">
+        <v>6</v>
+      </c>
+      <c r="E67" s="2">
+        <v>2</v>
+      </c>
+      <c r="F67" s="4">
+        <v>61000054</v>
+      </c>
+      <c r="G67" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="H67" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="I67" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="J67" s="6" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="68" customHeight="1" spans="3:10">
+      <c r="C68" s="2">
+        <v>55</v>
+      </c>
+      <c r="D68" s="2">
+        <v>6</v>
+      </c>
+      <c r="E68" s="2">
+        <v>2</v>
+      </c>
+      <c r="F68" s="4">
+        <v>61000055</v>
+      </c>
+      <c r="G68" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="H68" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="I68" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="J68" s="6" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="69" customHeight="1" spans="3:10">
+      <c r="C69" s="2">
+        <v>56</v>
+      </c>
+      <c r="D69" s="2">
+        <v>6</v>
+      </c>
+      <c r="E69" s="2">
+        <v>2</v>
+      </c>
+      <c r="F69" s="4">
+        <v>61000056</v>
+      </c>
+      <c r="G69" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="H69" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="I69" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="J69" s="6" t="s">
+        <v>70</v>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="E3 E4 E5 C3:D5 F3:G5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:G5" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/RelicConfig.xlsx
+++ b/Excel/RelicConfig.xlsx
@@ -2749,7 +2749,7 @@
         <v>49</v>
       </c>
       <c r="D62" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E62" s="2">
         <v>2</v>
@@ -2775,7 +2775,7 @@
         <v>50</v>
       </c>
       <c r="D63" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E63" s="2">
         <v>2</v>
@@ -2801,7 +2801,7 @@
         <v>51</v>
       </c>
       <c r="D64" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E64" s="2">
         <v>2</v>
@@ -2827,7 +2827,7 @@
         <v>52</v>
       </c>
       <c r="D65" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E65" s="2">
         <v>2</v>
@@ -2853,7 +2853,7 @@
         <v>53</v>
       </c>
       <c r="D66" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E66" s="2">
         <v>2</v>
@@ -2879,7 +2879,7 @@
         <v>54</v>
       </c>
       <c r="D67" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E67" s="2">
         <v>2</v>
@@ -2905,7 +2905,7 @@
         <v>55</v>
       </c>
       <c r="D68" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E68" s="2">
         <v>2</v>
@@ -2931,7 +2931,7 @@
         <v>56</v>
       </c>
       <c r="D69" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E69" s="2">
         <v>2</v>

--- a/Excel/RelicConfig.xlsx
+++ b/Excel/RelicConfig.xlsx
@@ -1,8 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\WrittenLegend\Excel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView windowHeight="17680"/>
   </bookViews>
@@ -27,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="94">
   <si>
     <t>#</t>
   </si>
@@ -285,6 +290,30 @@
   </si>
   <si>
     <t>极虎战靴</t>
+  </si>
+  <si>
+    <t>极雀神剑</t>
+  </si>
+  <si>
+    <t>极雀神甲</t>
+  </si>
+  <si>
+    <t>极雀面罩</t>
+  </si>
+  <si>
+    <t>极雀项链</t>
+  </si>
+  <si>
+    <t>极雀护腕</t>
+  </si>
+  <si>
+    <t>极雀护戒</t>
+  </si>
+  <si>
+    <t>极雀腰带</t>
+  </si>
+  <si>
+    <t>极雀战靴</t>
   </si>
 </sst>
 </file>
@@ -1258,7 +1287,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N69"/>
+  <dimension ref="A1:N78"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="5" width="9" style="1"/>
@@ -2952,6 +2981,214 @@
         <v>70</v>
       </c>
     </row>
+    <row r="71" customHeight="1" spans="3:10">
+      <c r="C71" s="2">
+        <v>57</v>
+      </c>
+      <c r="D71" s="2">
+        <v>8</v>
+      </c>
+      <c r="E71" s="2">
+        <v>2</v>
+      </c>
+      <c r="F71" s="4">
+        <v>61000057</v>
+      </c>
+      <c r="G71" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="H71" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="I71" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="J71" s="6" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="72" customHeight="1" spans="3:10">
+      <c r="C72" s="2">
+        <v>58</v>
+      </c>
+      <c r="D72" s="2">
+        <v>8</v>
+      </c>
+      <c r="E72" s="2">
+        <v>2</v>
+      </c>
+      <c r="F72" s="4">
+        <v>61000058</v>
+      </c>
+      <c r="G72" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="H72" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="I72" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="J72" s="6" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="73" customHeight="1" spans="3:10">
+      <c r="C73" s="2">
+        <v>59</v>
+      </c>
+      <c r="D73" s="2">
+        <v>8</v>
+      </c>
+      <c r="E73" s="2">
+        <v>2</v>
+      </c>
+      <c r="F73" s="4">
+        <v>61000059</v>
+      </c>
+      <c r="G73" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="H73" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="I73" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="J73" s="6" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="74" customHeight="1" spans="3:10">
+      <c r="C74" s="2">
+        <v>60</v>
+      </c>
+      <c r="D74" s="2">
+        <v>8</v>
+      </c>
+      <c r="E74" s="2">
+        <v>2</v>
+      </c>
+      <c r="F74" s="4">
+        <v>61000060</v>
+      </c>
+      <c r="G74" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="H74" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="I74" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="J74" s="6" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="75" customHeight="1" spans="3:10">
+      <c r="C75" s="2">
+        <v>61</v>
+      </c>
+      <c r="D75" s="2">
+        <v>8</v>
+      </c>
+      <c r="E75" s="2">
+        <v>2</v>
+      </c>
+      <c r="F75" s="4">
+        <v>61000061</v>
+      </c>
+      <c r="G75" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="H75" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="I75" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="J75" s="6" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="76" customHeight="1" spans="3:10">
+      <c r="C76" s="2">
+        <v>62</v>
+      </c>
+      <c r="D76" s="2">
+        <v>8</v>
+      </c>
+      <c r="E76" s="2">
+        <v>2</v>
+      </c>
+      <c r="F76" s="4">
+        <v>61000062</v>
+      </c>
+      <c r="G76" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="H76" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="I76" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="J76" s="6" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="77" customHeight="1" spans="3:10">
+      <c r="C77" s="2">
+        <v>63</v>
+      </c>
+      <c r="D77" s="2">
+        <v>8</v>
+      </c>
+      <c r="E77" s="2">
+        <v>2</v>
+      </c>
+      <c r="F77" s="4">
+        <v>61000063</v>
+      </c>
+      <c r="G77" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="H77" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="I77" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="J77" s="6" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="78" customHeight="1" spans="3:10">
+      <c r="C78" s="2">
+        <v>64</v>
+      </c>
+      <c r="D78" s="2">
+        <v>8</v>
+      </c>
+      <c r="E78" s="2">
+        <v>2</v>
+      </c>
+      <c r="F78" s="4">
+        <v>61000064</v>
+      </c>
+      <c r="G78" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="H78" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="I78" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="J78" s="6" t="s">
+        <v>70</v>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:G5" errorStyle="warning">
